--- a/docs/TestCases.xlsx
+++ b/docs/TestCases.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10306"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Abdelrahman Elhagali\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{879957AB-0DC2-4E3D-85FC-B86F822FC745}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{8D73E7BA-7837-124F-AEB3-8D20C066552F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{CF304ACA-5F53-4289-A851-278A9009C16C}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -41,31 +41,31 @@
     <t>ID</t>
   </si>
   <si>
+    <t>Title</t>
+  </si>
+  <si>
+    <t>Preconditions</t>
+  </si>
+  <si>
+    <t>Steps</t>
+  </si>
+  <si>
+    <t>Test Data</t>
+  </si>
+  <si>
+    <t>Expected Result</t>
+  </si>
+  <si>
+    <t>Actual Result</t>
+  </si>
+  <si>
+    <t>Status</t>
+  </si>
+  <si>
+    <t>Priority</t>
+  </si>
+  <si>
     <t>TC-01</t>
-  </si>
-  <si>
-    <t>Title</t>
-  </si>
-  <si>
-    <t>Preconditions</t>
-  </si>
-  <si>
-    <t>Steps</t>
-  </si>
-  <si>
-    <t>Test Data</t>
-  </si>
-  <si>
-    <t>Expected Result</t>
-  </si>
-  <si>
-    <t>Actual Result</t>
-  </si>
-  <si>
-    <t>Status</t>
-  </si>
-  <si>
-    <t>pass</t>
   </si>
   <si>
     <t>Generate Exam with Valid Inputs</t>
@@ -85,82 +85,130 @@
     <t>New record in Exam table and exactly 10 records in ExamQuestion table.</t>
   </si>
   <si>
+    <t>Exam generated successfully.</t>
+  </si>
+  <si>
+    <t>pass</t>
+  </si>
+  <si>
+    <t>Critical</t>
+  </si>
+  <si>
     <t>TC-02</t>
   </si>
   <si>
-    <t>TC-03</t>
-  </si>
-  <si>
-    <t>TC-04</t>
-  </si>
-  <si>
-    <t>TC-05</t>
-  </si>
-  <si>
-    <t>TC-06</t>
-  </si>
-  <si>
-    <t>TC-07</t>
-  </si>
-  <si>
-    <t>TC-08</t>
-  </si>
-  <si>
     <t>Course has limited questions (e.g., only 10 MCQ).</t>
-  </si>
-  <si>
-    <t>Submit All Exam Answers via XML</t>
-  </si>
-  <si>
-    <t>Submit Partial Exam Answers (Skipping Questions)</t>
-  </si>
-  <si>
-    <t>Calculate Grade for All Correct Answers</t>
-  </si>
-  <si>
-    <t>Calculate Grade for All Wrong Answers</t>
-  </si>
-  <si>
-    <t>Run System Reports</t>
-  </si>
-  <si>
-    <t>Delete Course with Existing Exams</t>
-  </si>
-  <si>
-    <t>Exam generated successfully.</t>
-  </si>
-  <si>
-    <t>Valid StudentID and ExamID exist.</t>
-  </si>
-  <si>
-    <t>A Course exists and has several Exam and Question records.</t>
-  </si>
-  <si>
-    <t>Tables contain sample data for Students, Instructors, and Grades.</t>
-  </si>
-  <si>
-    <t>Student has submitted answers that do not match any ModelAnswer.</t>
-  </si>
-  <si>
-    <t>Student has submitted answers that exactly match the ModelAnswer</t>
-  </si>
-  <si>
-    <t>Call CorrectExam with the StudentExamID.</t>
-  </si>
-  <si>
-    <t>Call CorrectExam.</t>
   </si>
   <si>
     <t>1.Call GenerateExam procedure.
 2.Request a number of questions higher than available.</t>
   </si>
   <si>
+    <t>NumMCQ = 200</t>
+  </si>
+  <si>
+    <t>Procedure throws an error: "Not enough questions in the bank...". No exam record is created.</t>
+  </si>
+  <si>
+    <t>Error raised as expected.</t>
+  </si>
+  <si>
+    <t>High</t>
+  </si>
+  <si>
+    <t>TC-03</t>
+  </si>
+  <si>
+    <t>Submit All Exam Answers via XML</t>
+  </si>
+  <si>
+    <t>Valid StudentID and ExamID exist.</t>
+  </si>
+  <si>
     <t>1.Prepare XML containing all question IDs and chosen options.
 2.Call SubmitExamAnswers procedure.</t>
   </si>
   <si>
+    <t>Answers = '&lt;Answers&gt;&lt;Answer&gt;...&lt;/Answer&gt;&lt;/Answers&gt;'</t>
+  </si>
+  <si>
+    <t>Record created in StudentExam and multiple records in StudentAnswer.</t>
+  </si>
+  <si>
+    <t>Submission completed successfully.</t>
+  </si>
+  <si>
+    <t>TC-04</t>
+  </si>
+  <si>
+    <t>Submit Partial Exam Answers (Skipping Questions)</t>
+  </si>
+  <si>
     <t>1.Prepare XML with only 1 answer for a multi-question exam.
 2.Call SubmitExamAnswers.</t>
+  </si>
+  <si>
+    <t>XML containing only one &lt;Answer&gt; block</t>
+  </si>
+  <si>
+    <t>StudentExam created; StudentAnswer contains only 1 row.</t>
+  </si>
+  <si>
+    <t>Successfully recorded only provided answers.</t>
+  </si>
+  <si>
+    <t>TC-05</t>
+  </si>
+  <si>
+    <t>Calculate Grade for All Correct Answers</t>
+  </si>
+  <si>
+    <t>Student has submitted answers that exactly match the ModelAnswer</t>
+  </si>
+  <si>
+    <t>Call CorrectExam with the StudentExamID.</t>
+  </si>
+  <si>
+    <t>StudentAnswer.ChosenOptionID = ModelAnswer.OptionID</t>
+  </si>
+  <si>
+    <t>TotalGrade in StudentExam equals the sum of all question points.</t>
+  </si>
+  <si>
+    <t>Full marks awarded.</t>
+  </si>
+  <si>
+    <t>TC-06</t>
+  </si>
+  <si>
+    <t>Calculate Grade for All Wrong Answers</t>
+  </si>
+  <si>
+    <t>Student has submitted answers that do not match any ModelAnswer.</t>
+  </si>
+  <si>
+    <t>Call CorrectExam.</t>
+  </si>
+  <si>
+    <t>All ChosenOptionID values are incorrect.</t>
+  </si>
+  <si>
+    <t>TotalGrade in StudentExam must be 0.</t>
+  </si>
+  <si>
+    <t>Grade updated to 0.</t>
+  </si>
+  <si>
+    <t>Medium</t>
+  </si>
+  <si>
+    <t>TC-07</t>
+  </si>
+  <si>
+    <t>Run System Reports</t>
+  </si>
+  <si>
+    <t>Tables contain sample data for Students, Instructors, and Grades.</t>
   </si>
   <si>
     <t>1.Execute Report_StudentsByDepartment.
@@ -168,82 +216,34 @@
 3.Execute Report_InstructorCourses.</t>
   </si>
   <si>
+    <t>Valid DepartmentNo, StudentID, and InstructorID.</t>
+  </si>
+  <si>
+    <t>Accurate data sets returned matching the input filters.</t>
+  </si>
+  <si>
+    <t>Correct data retrieved per report.</t>
+  </si>
+  <si>
+    <t>TC-08</t>
+  </si>
+  <si>
+    <t>Delete Course with Existing Exams</t>
+  </si>
+  <si>
+    <t>A Course exists and has several Exam and Question records.</t>
+  </si>
+  <si>
     <t>Delete the record from Course table.</t>
   </si>
   <si>
     <t>DELETE FROM Course WHERE CourseID = 1</t>
   </si>
   <si>
-    <t>Valid DepartmentNo, StudentID, and InstructorID.</t>
-  </si>
-  <si>
-    <t>All ChosenOptionID values are incorrect.</t>
-  </si>
-  <si>
-    <t>StudentAnswer.ChosenOptionID = ModelAnswer.OptionID</t>
-  </si>
-  <si>
-    <t>XML containing only one &lt;Answer&gt; block</t>
-  </si>
-  <si>
-    <t>Answers = '&lt;Answers&gt;&lt;Answer&gt;...&lt;/Answer&gt;&lt;/Answers&gt;'</t>
-  </si>
-  <si>
-    <t>NumMCQ = 200</t>
-  </si>
-  <si>
-    <t>Procedure throws an error: "Not enough questions in the bank...". No exam record is created.</t>
-  </si>
-  <si>
-    <t>Error raised as expected.</t>
-  </si>
-  <si>
-    <t>Record created in StudentExam and multiple records in StudentAnswer.</t>
-  </si>
-  <si>
-    <t>Submission completed successfully.</t>
-  </si>
-  <si>
-    <t>StudentExam created; StudentAnswer contains only 1 row.</t>
-  </si>
-  <si>
-    <t>Successfully recorded only provided answers.</t>
-  </si>
-  <si>
-    <t>TotalGrade in StudentExam equals the sum of all question points.</t>
-  </si>
-  <si>
-    <t>Full marks awarded.</t>
-  </si>
-  <si>
-    <t>TotalGrade in StudentExam must be 0.</t>
-  </si>
-  <si>
-    <t>Grade updated to 0.</t>
-  </si>
-  <si>
-    <t>Accurate data sets returned matching the input filters.</t>
-  </si>
-  <si>
-    <t>Correct data retrieved per report.</t>
-  </si>
-  <si>
-    <t>Due to ON DELETE CASCADE, all related Exams and Questions are automatically deleted.</t>
-  </si>
-  <si>
-    <t>Records cleared from child tables.</t>
-  </si>
-  <si>
-    <t>Priority</t>
-  </si>
-  <si>
-    <t>High</t>
-  </si>
-  <si>
-    <t>Critical</t>
-  </si>
-  <si>
-    <t>Medium</t>
+    <t>SQL Server throws a Foreign Key constraint error and the deletion is rejected, protecting student exam history.</t>
+  </si>
+  <si>
+    <t>Error raised as expected. Record was not deleted.</t>
   </si>
 </sst>
 </file>
@@ -734,51 +734,51 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B2A720D6-F7CE-4DE8-900E-77B24F0A27E3}">
   <dimension ref="A1:I9"/>
-  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8.88671875" style="5"/>
-    <col min="2" max="2" width="35.5546875" customWidth="1"/>
-    <col min="3" max="3" width="22.44140625" customWidth="1"/>
-    <col min="4" max="4" width="20" style="10" customWidth="1"/>
-    <col min="5" max="5" width="18.6640625" style="10" customWidth="1"/>
-    <col min="6" max="6" width="32" style="12" customWidth="1"/>
-    <col min="7" max="7" width="23.44140625" style="12" customWidth="1"/>
-    <col min="8" max="8" width="14.5546875" customWidth="1"/>
-    <col min="9" max="9" width="13" customWidth="1"/>
+    <col min="1" max="1" width="8.875" style="5"/>
+    <col min="2" max="2" width="35.51171875" customWidth="1"/>
+    <col min="3" max="3" width="22.46484375" customWidth="1"/>
+    <col min="4" max="4" width="20.04296875" style="10" customWidth="1"/>
+    <col min="5" max="5" width="18.6953125" style="10" customWidth="1"/>
+    <col min="6" max="6" width="32.015625" style="12" customWidth="1"/>
+    <col min="7" max="7" width="23.40625" style="12" customWidth="1"/>
+    <col min="8" max="8" width="14.52734375" customWidth="1"/>
+    <col min="9" max="9" width="13.046875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" s="1" customFormat="1" ht="23.4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" s="1" customFormat="1" ht="24.75" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="D1" s="13" t="s">
+      <c r="E1" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="13" t="s">
+      <c r="F1" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="F1" s="13" t="s">
+      <c r="G1" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="G1" s="13" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="I1" s="1" t="s">
-        <v>63</v>
-      </c>
     </row>
-    <row r="2" spans="1:9" s="9" customFormat="1" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:9" s="9" customFormat="1" ht="81" x14ac:dyDescent="0.2">
       <c r="A2" s="3" t="s">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="B2" s="7" t="s">
         <v>10</v>
@@ -796,216 +796,216 @@
         <v>14</v>
       </c>
       <c r="G2" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="H2" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="I2" s="15" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" ht="81.75" x14ac:dyDescent="0.25">
+      <c r="A3" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="C3" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="D3" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="E3" s="11" t="s">
+        <v>21</v>
+      </c>
+      <c r="F3" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="G3" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="H3" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="I3" s="14" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" ht="95.25" x14ac:dyDescent="0.25">
+      <c r="A4" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="C4" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="D4" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="E4" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="H2" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="I2" s="15" t="s">
+      <c r="F4" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="G4" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="H4" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="I4" s="14" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" ht="81.75" x14ac:dyDescent="0.25">
+      <c r="A5" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="C5" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="D5" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="E5" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="F5" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="G5" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="H5" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="I5" s="14" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" ht="55.5" x14ac:dyDescent="0.25">
+      <c r="A6" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="C6" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="D6" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="E6" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="F6" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="G6" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="H6" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="I6" s="14" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" ht="42" x14ac:dyDescent="0.25">
+      <c r="A7" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="C7" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="D7" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="E7" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="F7" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="G7" s="12" t="s">
+        <v>51</v>
+      </c>
+      <c r="H7" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="I7" s="16" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" ht="135.75" x14ac:dyDescent="0.25">
+      <c r="A8" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="C8" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="D8" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="E8" s="12" t="s">
+        <v>57</v>
+      </c>
+      <c r="F8" s="12" t="s">
+        <v>58</v>
+      </c>
+      <c r="G8" s="12" t="s">
+        <v>59</v>
+      </c>
+      <c r="H8" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="I8" s="14" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" ht="55.5" x14ac:dyDescent="0.25">
+      <c r="A9" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="C9" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="D9" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="E9" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="F9" s="12" t="s">
         <v>65</v>
       </c>
-    </row>
-    <row r="3" spans="1:9" ht="86.4" x14ac:dyDescent="0.35">
-      <c r="A3" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="B3" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="C3" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="D3" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="E3" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="F3" s="11" t="s">
-        <v>49</v>
-      </c>
-      <c r="G3" s="11" t="s">
-        <v>50</v>
-      </c>
-      <c r="H3" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="I3" s="14" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" ht="115.2" x14ac:dyDescent="0.35">
-      <c r="A4" s="5" t="s">
+      <c r="G9" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="H9" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="B4" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="C4" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="D4" s="11" t="s">
-        <v>38</v>
-      </c>
-      <c r="E4" s="11" t="s">
-        <v>47</v>
-      </c>
-      <c r="F4" s="12" t="s">
-        <v>51</v>
-      </c>
-      <c r="G4" s="12" t="s">
-        <v>52</v>
-      </c>
-      <c r="H4" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="I4" s="14" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" ht="86.4" x14ac:dyDescent="0.35">
-      <c r="A5" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="B5" s="7" t="s">
+      <c r="I9" s="14" t="s">
         <v>24</v>
-      </c>
-      <c r="C5" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="D5" s="11" t="s">
-        <v>39</v>
-      </c>
-      <c r="E5" s="11" t="s">
-        <v>46</v>
-      </c>
-      <c r="F5" s="12" t="s">
-        <v>53</v>
-      </c>
-      <c r="G5" s="12" t="s">
-        <v>54</v>
-      </c>
-      <c r="H5" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="I5" s="14" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" ht="57.6" x14ac:dyDescent="0.35">
-      <c r="A6" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="B6" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="C6" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="D6" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="E6" s="11" t="s">
-        <v>45</v>
-      </c>
-      <c r="F6" s="12" t="s">
-        <v>55</v>
-      </c>
-      <c r="G6" s="12" t="s">
-        <v>56</v>
-      </c>
-      <c r="H6" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="I6" s="14" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" ht="43.2" x14ac:dyDescent="0.35">
-      <c r="A7" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="B7" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="C7" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="D7" s="11" t="s">
-        <v>36</v>
-      </c>
-      <c r="E7" s="11" t="s">
-        <v>44</v>
-      </c>
-      <c r="F7" s="12" t="s">
-        <v>57</v>
-      </c>
-      <c r="G7" s="12" t="s">
-        <v>58</v>
-      </c>
-      <c r="H7" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="I7" s="16" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" ht="144" x14ac:dyDescent="0.35">
-      <c r="A8" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="B8" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="C8" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="D8" s="11" t="s">
-        <v>40</v>
-      </c>
-      <c r="E8" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="F8" s="12" t="s">
-        <v>59</v>
-      </c>
-      <c r="G8" s="12" t="s">
-        <v>60</v>
-      </c>
-      <c r="H8" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="I8" s="14" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" ht="43.2" x14ac:dyDescent="0.35">
-      <c r="A9" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="C9" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="D9" s="11" t="s">
-        <v>41</v>
-      </c>
-      <c r="E9" s="10" t="s">
-        <v>42</v>
-      </c>
-      <c r="F9" s="12" t="s">
-        <v>61</v>
-      </c>
-      <c r="G9" s="12" t="s">
-        <v>62</v>
-      </c>
-      <c r="H9" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="I9" s="14" t="s">
-        <v>64</v>
       </c>
     </row>
   </sheetData>
